--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -865,7 +865,7 @@
     <t>0.4591,0.0312,0.3586,0.0042</t>
   </si>
   <si>
-    <t>0.8081,0.0003,0.2470,0.0001</t>
+    <t>0.8080,0.0003,0.2470,0.0001</t>
   </si>
   <si>
     <t>0.3139,0.0041,0.6872,0.0025</t>
@@ -901,7 +901,7 @@
     <t>0.3688,0.0018,0.6302,0.0010</t>
   </si>
   <si>
-    <t>0.3357,0.0006,0.6957,0.0007</t>
+    <t>0.3356,0.0006,0.6957,0.0007</t>
   </si>
   <si>
     <t>0.4531,0.0001,0.6593,0.0001</t>
@@ -1012,7 +1012,7 @@
     <t>0.0086,0.0103,0.9843,0.0024</t>
   </si>
   <si>
-    <t>0.0009,0.9713,0.8393,0.0007</t>
+    <t>0.0009,0.9713,0.8392,0.0007</t>
   </si>
   <si>
     <t>0.0002,0.0001,0.9998,0.0001</t>
@@ -1297,7 +1297,7 @@
     <t>0.9863,0.0064,0.0028,0.0001</t>
   </si>
   <si>
-    <t>0.2252,0.8497,0.0036,0.0003</t>
+    <t>0.2252,0.8498,0.0036,0.0003</t>
   </si>
   <si>
     <t>0.9565,0.0278,0.0091,0.0001</t>
@@ -1327,7 +1327,7 @@
     <t>0.9979,0.0003,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.5803,0.5227,0.0082,0.0009</t>
+    <t>0.5803,0.5228,0.0082,0.0009</t>
   </si>
   <si>
     <t>0.6083,0.5229,0.0029,0.0002</t>
@@ -1351,7 +1351,7 @@
     <t>0.9872,0.0091,0.0017,0.0000</t>
   </si>
   <si>
-    <t>0.2856,0.0014,0.8575,0.0004</t>
+    <t>0.2856,0.0014,0.8574,0.0004</t>
   </si>
   <si>
     <t>0.9808,0.0077,0.0053,0.0001</t>
@@ -1402,10 +1402,10 @@
     <t>0.7961,0.0335,0.0826,0.0017</t>
   </si>
   <si>
-    <t>0.1404,0.9390,0.0105,0.0002</t>
-  </si>
-  <si>
-    <t>0.3788,0.8336,0.0002,0.0000</t>
+    <t>0.1403,0.9390,0.0105,0.0002</t>
+  </si>
+  <si>
+    <t>0.3788,0.8337,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.8554,0.2598,0.0005,0.0000</t>
@@ -1471,7 +1471,7 @@
     <t>0.9948,0.0001,0.0021,0.0001</t>
   </si>
   <si>
-    <t>0.5677,0.0011,0.5408,0.0004</t>
+    <t>0.5677,0.0011,0.5407,0.0004</t>
   </si>
   <si>
     <t>0.9059,0.0189,0.0413,0.0002</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -814,6 +814,9 @@
     <t>0,0,0,1</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,0</t>
   </si>
   <si>
@@ -823,16 +826,22 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9559,0.0017,0.0149,0.0020</t>
-  </si>
-  <si>
-    <t>0.2331,0.0002,0.0005,0.9006</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9559,0.0017,0.0150,0.0020</t>
+  </si>
+  <si>
+    <t>0.2329,0.0002,0.0005,0.9008</t>
   </si>
   <si>
     <t>0.9883,0.0006,0.0006,0.0014</t>
   </si>
   <si>
-    <t>0.8856,0.0001,0.0028,0.0560</t>
+    <t>0.8854,0.0001,0.0028,0.0562</t>
   </si>
   <si>
     <t>0.9986,0.0001,0.0004,0.0000</t>
@@ -862,16 +871,16 @@
     <t>0.9379,0.0043,0.0280,0.0005</t>
   </si>
   <si>
-    <t>0.4591,0.0312,0.3586,0.0042</t>
-  </si>
-  <si>
-    <t>0.8080,0.0003,0.2470,0.0001</t>
-  </si>
-  <si>
-    <t>0.3139,0.0041,0.6872,0.0025</t>
-  </si>
-  <si>
-    <t>0.9644,0.0003,0.0250,0.0000</t>
+    <t>0.4587,0.0312,0.3589,0.0042</t>
+  </si>
+  <si>
+    <t>0.8079,0.0003,0.2472,0.0001</t>
+  </si>
+  <si>
+    <t>0.3138,0.0041,0.6872,0.0025</t>
+  </si>
+  <si>
+    <t>0.9643,0.0003,0.0251,0.0000</t>
   </si>
   <si>
     <t>0.0015,0.9991,0.0019,0.0001</t>
@@ -889,73 +898,73 @@
     <t>0.0013,0.9992,0.0068,0.0001</t>
   </si>
   <si>
-    <t>0.8909,0.0007,0.0775,0.0005</t>
-  </si>
-  <si>
-    <t>0.4625,0.0175,0.4079,0.0056</t>
-  </si>
-  <si>
-    <t>0.3049,0.0002,0.7658,0.0001</t>
-  </si>
-  <si>
-    <t>0.3688,0.0018,0.6302,0.0010</t>
-  </si>
-  <si>
-    <t>0.3356,0.0006,0.6957,0.0007</t>
-  </si>
-  <si>
-    <t>0.4531,0.0001,0.6593,0.0001</t>
+    <t>0.8907,0.0007,0.0777,0.0005</t>
+  </si>
+  <si>
+    <t>0.4619,0.0176,0.4086,0.0056</t>
+  </si>
+  <si>
+    <t>0.3046,0.0002,0.7659,0.0001</t>
+  </si>
+  <si>
+    <t>0.3685,0.0018,0.6304,0.0010</t>
+  </si>
+  <si>
+    <t>0.3354,0.0006,0.6958,0.0007</t>
+  </si>
+  <si>
+    <t>0.4527,0.0001,0.6596,0.0001</t>
   </si>
   <si>
     <t>0.0534,0.0000,0.9758,0.0001</t>
   </si>
   <si>
-    <t>0.9251,0.0733,0.0068,0.0001</t>
-  </si>
-  <si>
-    <t>0.9535,0.0496,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.0053,0.0001,0.9971,0.0007</t>
-  </si>
-  <si>
-    <t>0.3409,0.0655,0.4386,0.0014</t>
-  </si>
-  <si>
-    <t>0.9867,0.0011,0.0056,0.0002</t>
-  </si>
-  <si>
-    <t>0.9586,0.0147,0.0116,0.0002</t>
-  </si>
-  <si>
-    <t>0.7653,0.3525,0.0109,0.0004</t>
-  </si>
-  <si>
-    <t>0.0806,0.8984,0.1857,0.0013</t>
-  </si>
-  <si>
-    <t>0.0010,0.6208,0.9764,0.0003</t>
-  </si>
-  <si>
-    <t>0.0041,0.0024,0.9949,0.0008</t>
-  </si>
-  <si>
-    <t>0.0897,0.0159,0.8710,0.0038</t>
-  </si>
-  <si>
-    <t>0.3200,0.0010,0.6219,0.0153</t>
-  </si>
-  <si>
-    <t>0.0094,0.5016,0.9022,0.0014</t>
+    <t>0.9250,0.0734,0.0068,0.0001</t>
+  </si>
+  <si>
+    <t>0.9533,0.0497,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.0002,0.9971,0.0007</t>
+  </si>
+  <si>
+    <t>0.3402,0.0656,0.4392,0.0014</t>
+  </si>
+  <si>
+    <t>0.9867,0.0011,0.0057,0.0002</t>
+  </si>
+  <si>
+    <t>0.9586,0.0148,0.0117,0.0002</t>
+  </si>
+  <si>
+    <t>0.7651,0.3527,0.0109,0.0004</t>
+  </si>
+  <si>
+    <t>0.0805,0.8983,0.1860,0.0013</t>
+  </si>
+  <si>
+    <t>0.0010,0.6214,0.9764,0.0003</t>
+  </si>
+  <si>
+    <t>0.0041,0.0024,0.9949,0.0009</t>
+  </si>
+  <si>
+    <t>0.0896,0.0159,0.8710,0.0038</t>
+  </si>
+  <si>
+    <t>0.3198,0.0010,0.6221,0.0154</t>
+  </si>
+  <si>
+    <t>0.0093,0.5025,0.9022,0.0014</t>
   </si>
   <si>
     <t>0.0153,0.9845,0.0209,0.0002</t>
   </si>
   <si>
-    <t>0.0198,0.0092,0.9744,0.0021</t>
-  </si>
-  <si>
-    <t>0.0046,0.8481,0.0006,0.3319</t>
+    <t>0.0197,0.0092,0.9744,0.0021</t>
+  </si>
+  <si>
+    <t>0.0046,0.8482,0.0006,0.3321</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0002,0.0000</t>
@@ -970,19 +979,19 @@
     <t>0.0013,0.0091,0.9973,0.0004</t>
   </si>
   <si>
-    <t>0.0037,0.2110,0.9679,0.0024</t>
+    <t>0.0037,0.2117,0.9679,0.0024</t>
   </si>
   <si>
     <t>0.0348,0.0005,0.9742,0.0011</t>
   </si>
   <si>
-    <t>0.6005,0.0000,0.5569,0.0000</t>
-  </si>
-  <si>
-    <t>0.1553,0.0008,0.8789,0.0003</t>
-  </si>
-  <si>
-    <t>0.1278,0.0105,0.8140,0.0031</t>
+    <t>0.6001,0.0000,0.5573,0.0000</t>
+  </si>
+  <si>
+    <t>0.1552,0.0008,0.8790,0.0003</t>
+  </si>
+  <si>
+    <t>0.1277,0.0105,0.8140,0.0031</t>
   </si>
   <si>
     <t>0.9938,0.0020,0.0013,0.0000</t>
@@ -994,7 +1003,7 @@
     <t>0.9928,0.0013,0.0024,0.0002</t>
   </si>
   <si>
-    <t>0.7964,0.0002,0.2762,0.0003</t>
+    <t>0.7960,0.0002,0.2768,0.0003</t>
   </si>
   <si>
     <t>0.9963,0.0001,0.0016,0.0000</t>
@@ -1003,16 +1012,16 @@
     <t>0.9960,0.0004,0.0016,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.9966,0.6434,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0162,0.9965,0.0002</t>
+    <t>0.0003,0.9967,0.6438,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0163,0.9965,0.0002</t>
   </si>
   <si>
     <t>0.0086,0.0103,0.9843,0.0024</t>
   </si>
   <si>
-    <t>0.0009,0.9713,0.8392,0.0007</t>
+    <t>0.0009,0.9714,0.8393,0.0007</t>
   </si>
   <si>
     <t>0.0002,0.0001,0.9998,0.0001</t>
@@ -1027,22 +1036,22 @@
     <t>0.9918,0.0003,0.0044,0.0000</t>
   </si>
   <si>
-    <t>0.7731,0.0450,0.1505,0.0020</t>
-  </si>
-  <si>
-    <t>0.1018,0.0025,0.9273,0.0004</t>
-  </si>
-  <si>
-    <t>0.0037,0.9177,0.8186,0.0009</t>
-  </si>
-  <si>
-    <t>0.0015,0.7960,0.9500,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0820,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9291,0.9061,0.0010</t>
+    <t>0.7727,0.0451,0.1509,0.0020</t>
+  </si>
+  <si>
+    <t>0.1017,0.0025,0.9273,0.0004</t>
+  </si>
+  <si>
+    <t>0.0037,0.9179,0.8186,0.0009</t>
+  </si>
+  <si>
+    <t>0.0015,0.7962,0.9500,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0822,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9292,0.9062,0.0010</t>
   </si>
   <si>
     <t>0.0267,0.0007,0.0015,0.9881</t>
@@ -1051,34 +1060,34 @@
     <t>0.0413,0.0002,0.0004,0.9916</t>
   </si>
   <si>
-    <t>0.0576,0.0000,0.0002,0.9926</t>
-  </si>
-  <si>
-    <t>0.0446,0.0001,0.0017,0.9886</t>
-  </si>
-  <si>
-    <t>0.3470,0.0005,0.0009,0.6445</t>
+    <t>0.0575,0.0000,0.0002,0.9926</t>
+  </si>
+  <si>
+    <t>0.0445,0.0001,0.0017,0.9887</t>
+  </si>
+  <si>
+    <t>0.3469,0.0005,0.0009,0.6448</t>
   </si>
   <si>
     <t>0.0112,0.0003,0.0022,0.9972</t>
   </si>
   <si>
-    <t>0.0005,0.9954,0.6288,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.6042,0.9614,0.0008</t>
-  </si>
-  <si>
-    <t>0.0078,0.9533,0.2738,0.0010</t>
-  </si>
-  <si>
-    <t>0.0019,0.7202,0.9552,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.9938,0.7333,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.9951,0.2000,0.0002</t>
+    <t>0.0005,0.9954,0.6290,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.6048,0.9614,0.0008</t>
+  </si>
+  <si>
+    <t>0.0078,0.9534,0.2741,0.0010</t>
+  </si>
+  <si>
+    <t>0.0019,0.7207,0.9552,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.9938,0.7336,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.9951,0.2005,0.0002</t>
   </si>
   <si>
     <t>0.9990,0.0004,0.0001,0.0000</t>
@@ -1102,7 +1111,7 @@
     <t>0.9966,0.0003,0.0013,0.0000</t>
   </si>
   <si>
-    <t>0.8522,0.0037,0.0621,0.0032</t>
+    <t>0.8520,0.0037,0.0623,0.0032</t>
   </si>
   <si>
     <t>0.9987,0.0000,0.0004,0.0000</t>
@@ -1132,13 +1141,13 @@
     <t>0.0168,0.0000,0.9939,0.0001</t>
   </si>
   <si>
-    <t>0.4822,0.0055,0.4323,0.0013</t>
+    <t>0.4819,0.0055,0.4326,0.0013</t>
   </si>
   <si>
     <t>0.9895,0.0001,0.0067,0.0000</t>
   </si>
   <si>
-    <t>0.6009,0.0026,0.3106,0.0005</t>
+    <t>0.6004,0.0026,0.3110,0.0005</t>
   </si>
   <si>
     <t>0.0004,0.9999,0.0001,0.0000</t>
@@ -1147,7 +1156,7 @@
     <t>0.1327,0.9342,0.0020,0.0001</t>
   </si>
   <si>
-    <t>0.0448,0.9781,0.0029,0.0002</t>
+    <t>0.0448,0.9781,0.0029,0.0003</t>
   </si>
   <si>
     <t>0.0010,0.9996,0.0002,0.0000</t>
@@ -1156,22 +1165,22 @@
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7676,0.3730,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.7927,0.0275,0.0859,0.0017</t>
-  </si>
-  <si>
-    <t>0.2902,0.0060,0.6872,0.0041</t>
-  </si>
-  <si>
-    <t>0.8465,0.0088,0.0676,0.0005</t>
-  </si>
-  <si>
-    <t>0.8156,0.0101,0.1022,0.0018</t>
-  </si>
-  <si>
-    <t>0.0015,0.6014,0.6579,0.1304</t>
+    <t>0.7672,0.3735,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.7923,0.0275,0.0862,0.0017</t>
+  </si>
+  <si>
+    <t>0.2899,0.0060,0.6874,0.0041</t>
+  </si>
+  <si>
+    <t>0.8463,0.0088,0.0676,0.0005</t>
+  </si>
+  <si>
+    <t>0.8154,0.0101,0.1024,0.0018</t>
+  </si>
+  <si>
+    <t>0.0015,0.6013,0.6586,0.1300</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0010,0.0000</t>
@@ -1183,16 +1192,16 @@
     <t>0.0003,0.9994,0.0003,0.0007</t>
   </si>
   <si>
-    <t>0.0005,0.9991,0.0463,0.0001</t>
-  </si>
-  <si>
-    <t>0.0138,0.9875,0.1079,0.0007</t>
-  </si>
-  <si>
-    <t>0.4495,0.6463,0.0222,0.0006</t>
-  </si>
-  <si>
-    <t>0.1905,0.8718,0.0270,0.0023</t>
+    <t>0.0005,0.9991,0.0464,0.0001</t>
+  </si>
+  <si>
+    <t>0.0138,0.9875,0.1081,0.0007</t>
+  </si>
+  <si>
+    <t>0.4490,0.6468,0.0223,0.0006</t>
+  </si>
+  <si>
+    <t>0.1904,0.8719,0.0271,0.0023</t>
   </si>
   <si>
     <t>0.9980,0.0001,0.0006,0.0000</t>
@@ -1207,7 +1216,7 @@
     <t>0.9970,0.0002,0.0009,0.0000</t>
   </si>
   <si>
-    <t>0.9903,0.0020,0.0025,0.0012</t>
+    <t>0.9902,0.0020,0.0025,0.0012</t>
   </si>
   <si>
     <t>0.9973,0.0002,0.0008,0.0000</t>
@@ -1219,31 +1228,31 @@
     <t>0.9974,0.0001,0.0008,0.0000</t>
   </si>
   <si>
-    <t>0.0040,0.7950,0.8786,0.0013</t>
-  </si>
-  <si>
-    <t>0.0017,0.4410,0.9810,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.0439,0.9943,0.0005</t>
-  </si>
-  <si>
-    <t>0.0572,0.0053,0.9485,0.0009</t>
-  </si>
-  <si>
-    <t>0.9853,0.0005,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.8031,0.1447,0.0086,0.0003</t>
-  </si>
-  <si>
-    <t>0.6265,0.0001,0.4879,0.0004</t>
-  </si>
-  <si>
-    <t>0.8839,0.0071,0.0506,0.0008</t>
-  </si>
-  <si>
-    <t>0.2423,0.0000,0.0014,0.8885</t>
+    <t>0.0040,0.7953,0.8787,0.0013</t>
+  </si>
+  <si>
+    <t>0.0017,0.4417,0.9810,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0441,0.9943,0.0005</t>
+  </si>
+  <si>
+    <t>0.0571,0.0053,0.9486,0.0009</t>
+  </si>
+  <si>
+    <t>0.9852,0.0005,0.0052,0.0001</t>
+  </si>
+  <si>
+    <t>0.8028,0.1450,0.0086,0.0003</t>
+  </si>
+  <si>
+    <t>0.6261,0.0001,0.4883,0.0004</t>
+  </si>
+  <si>
+    <t>0.8838,0.0071,0.0506,0.0008</t>
+  </si>
+  <si>
+    <t>0.2419,0.0000,0.0014,0.8888</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.0004,1.0000</t>
@@ -1252,22 +1261,22 @@
     <t>0.0003,0.0000,0.0003,0.9999</t>
   </si>
   <si>
-    <t>0.1185,0.0001,0.0008,0.9480</t>
-  </si>
-  <si>
-    <t>0.0006,0.9929,0.6673,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0003,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.5450,0.5692,0.0023,0.0002</t>
+    <t>0.1184,0.0001,0.0008,0.9480</t>
+  </si>
+  <si>
+    <t>0.0006,0.9929,0.6677,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0003,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.5447,0.5694,0.0023,0.0002</t>
   </si>
   <si>
     <t>0.9977,0.0001,0.0006,0.0000</t>
   </si>
   <si>
-    <t>0.6662,0.5179,0.0012,0.0000</t>
+    <t>0.6657,0.5185,0.0012,0.0000</t>
   </si>
   <si>
     <t>0.9975,0.0001,0.0004,0.0001</t>
@@ -1282,13 +1291,13 @@
     <t>0.0000,0.0000,1.0000,0.0001</t>
   </si>
   <si>
-    <t>0.6990,0.0000,0.0890,0.0042</t>
+    <t>0.6992,0.0000,0.0890,0.0042</t>
   </si>
   <si>
     <t>0.9937,0.0003,0.0017,0.0001</t>
   </si>
   <si>
-    <t>0.9390,0.0405,0.0079,0.0002</t>
+    <t>0.9389,0.0406,0.0079,0.0002</t>
   </si>
   <si>
     <t>0.9963,0.0006,0.0008,0.0000</t>
@@ -1297,13 +1306,13 @@
     <t>0.9863,0.0064,0.0028,0.0001</t>
   </si>
   <si>
-    <t>0.2252,0.8498,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.9565,0.0278,0.0091,0.0001</t>
-  </si>
-  <si>
-    <t>0.9487,0.0073,0.0275,0.0004</t>
+    <t>0.2250,0.8499,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.9565,0.0278,0.0092,0.0001</t>
+  </si>
+  <si>
+    <t>0.9486,0.0074,0.0276,0.0004</t>
   </si>
   <si>
     <t>0.9983,0.0004,0.0003,0.0000</t>
@@ -1327,22 +1336,22 @@
     <t>0.9979,0.0003,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.5803,0.5228,0.0082,0.0009</t>
-  </si>
-  <si>
-    <t>0.6083,0.5229,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.8700,0.1516,0.0011,0.0001</t>
+    <t>0.5799,0.5232,0.0083,0.0009</t>
+  </si>
+  <si>
+    <t>0.6079,0.5234,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.8698,0.1520,0.0011,0.0001</t>
   </si>
   <si>
     <t>0.9909,0.0013,0.0040,0.0000</t>
   </si>
   <si>
-    <t>0.9962,0.0013,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9812,0.0047,0.0069,0.0001</t>
+    <t>0.9961,0.0013,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9812,0.0047,0.0070,0.0001</t>
   </si>
   <si>
     <t>0.9947,0.0003,0.0022,0.0001</t>
@@ -1351,7 +1360,7 @@
     <t>0.9872,0.0091,0.0017,0.0000</t>
   </si>
   <si>
-    <t>0.2856,0.0014,0.8574,0.0004</t>
+    <t>0.2854,0.0014,0.8575,0.0004</t>
   </si>
   <si>
     <t>0.9808,0.0077,0.0053,0.0001</t>
@@ -1360,16 +1369,16 @@
     <t>0.0068,0.0002,0.9967,0.0002</t>
   </si>
   <si>
-    <t>0.0026,0.0589,0.9894,0.0014</t>
-  </si>
-  <si>
-    <t>0.2145,0.0025,0.8336,0.0040</t>
-  </si>
-  <si>
-    <t>0.0105,0.0713,0.9606,0.0008</t>
-  </si>
-  <si>
-    <t>0.0112,0.0010,0.9933,0.0003</t>
+    <t>0.0026,0.0590,0.9894,0.0014</t>
+  </si>
+  <si>
+    <t>0.2141,0.0025,0.8338,0.0040</t>
+  </si>
+  <si>
+    <t>0.0105,0.0715,0.9606,0.0008</t>
+  </si>
+  <si>
+    <t>0.0111,0.0010,0.9933,0.0003</t>
   </si>
   <si>
     <t>0.0138,0.0000,0.9941,0.0001</t>
@@ -1378,73 +1387,73 @@
     <t>0.2505,0.0008,0.7986,0.0003</t>
   </si>
   <si>
-    <t>0.6867,0.0103,0.1869,0.0010</t>
-  </si>
-  <si>
-    <t>0.7517,0.0002,0.3044,0.0002</t>
-  </si>
-  <si>
-    <t>0.8594,0.0359,0.0358,0.0006</t>
-  </si>
-  <si>
-    <t>0.4865,0.0168,0.3599,0.0029</t>
-  </si>
-  <si>
-    <t>0.3139,0.0251,0.4998,0.0009</t>
-  </si>
-  <si>
-    <t>0.4353,0.0013,0.6235,0.0006</t>
-  </si>
-  <si>
-    <t>0.7720,0.0053,0.1407,0.0008</t>
-  </si>
-  <si>
-    <t>0.7961,0.0335,0.0826,0.0017</t>
+    <t>0.6865,0.0103,0.1872,0.0010</t>
+  </si>
+  <si>
+    <t>0.7514,0.0002,0.3047,0.0002</t>
+  </si>
+  <si>
+    <t>0.8593,0.0360,0.0359,0.0006</t>
+  </si>
+  <si>
+    <t>0.4861,0.0168,0.3603,0.0029</t>
+  </si>
+  <si>
+    <t>0.3135,0.0252,0.5001,0.0009</t>
+  </si>
+  <si>
+    <t>0.4351,0.0013,0.6236,0.0006</t>
+  </si>
+  <si>
+    <t>0.7717,0.0053,0.1409,0.0008</t>
+  </si>
+  <si>
+    <t>0.7959,0.0336,0.0827,0.0017</t>
   </si>
   <si>
     <t>0.1403,0.9390,0.0105,0.0002</t>
   </si>
   <si>
-    <t>0.3788,0.8337,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8554,0.2598,0.0005,0.0000</t>
+    <t>0.3785,0.8338,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8552,0.2602,0.0005,0.0000</t>
   </si>
   <si>
     <t>0.9946,0.0015,0.0014,0.0000</t>
   </si>
   <si>
-    <t>0.9868,0.0110,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.5300,0.5712,0.0035,0.0001</t>
+    <t>0.9868,0.0111,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.5295,0.5716,0.0036,0.0001</t>
   </si>
   <si>
     <t>0.9865,0.0007,0.0040,0.0001</t>
   </si>
   <si>
-    <t>0.7482,0.0261,0.1224,0.0054</t>
-  </si>
-  <si>
-    <t>0.4917,0.0008,0.4663,0.0044</t>
-  </si>
-  <si>
-    <t>0.9330,0.0045,0.0226,0.0002</t>
-  </si>
-  <si>
-    <t>0.1138,0.0003,0.9231,0.0006</t>
-  </si>
-  <si>
-    <t>0.3513,0.0052,0.6724,0.0051</t>
-  </si>
-  <si>
-    <t>0.2053,0.0443,0.6131,0.0017</t>
-  </si>
-  <si>
-    <t>0.0200,0.0037,0.9794,0.0009</t>
-  </si>
-  <si>
-    <t>0.0688,0.0107,0.8966,0.0006</t>
+    <t>0.7481,0.0262,0.1225,0.0054</t>
+  </si>
+  <si>
+    <t>0.4916,0.0008,0.4663,0.0044</t>
+  </si>
+  <si>
+    <t>0.9329,0.0045,0.0227,0.0002</t>
+  </si>
+  <si>
+    <t>0.1137,0.0003,0.9232,0.0006</t>
+  </si>
+  <si>
+    <t>0.3510,0.0053,0.6727,0.0051</t>
+  </si>
+  <si>
+    <t>0.2049,0.0445,0.6133,0.0017</t>
+  </si>
+  <si>
+    <t>0.0200,0.0038,0.9794,0.0009</t>
+  </si>
+  <si>
+    <t>0.0687,0.0108,0.8966,0.0006</t>
   </si>
   <si>
     <t>0.9972,0.0001,0.0010,0.0000</t>
@@ -1459,25 +1468,25 @@
     <t>0.9949,0.0037,0.0006,0.0001</t>
   </si>
   <si>
-    <t>0.9938,0.0029,0.0011,0.0000</t>
+    <t>0.9937,0.0029,0.0011,0.0000</t>
   </si>
   <si>
     <t>0.9968,0.0014,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.9968,0.0008,0.0008,0.0000</t>
+    <t>0.9967,0.0008,0.0008,0.0000</t>
   </si>
   <si>
     <t>0.9948,0.0001,0.0021,0.0001</t>
   </si>
   <si>
-    <t>0.5677,0.0011,0.5407,0.0004</t>
-  </si>
-  <si>
-    <t>0.9059,0.0189,0.0413,0.0002</t>
-  </si>
-  <si>
-    <t>0.9375,0.0033,0.0445,0.0007</t>
+    <t>0.5672,0.0011,0.5413,0.0004</t>
+  </si>
+  <si>
+    <t>0.9058,0.0189,0.0413,0.0002</t>
+  </si>
+  <si>
+    <t>0.9374,0.0033,0.0445,0.0007</t>
   </si>
   <si>
     <t>0.0022,0.0002,0.9986,0.0001</t>
@@ -1486,13 +1495,13 @@
     <t>0.0010,0.0008,0.9989,0.0002</t>
   </si>
   <si>
-    <t>0.0817,0.0266,0.8396,0.0020</t>
+    <t>0.0816,0.0266,0.8397,0.0020</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.2715,0.0074,0.6715,0.0011</t>
+    <t>0.2713,0.0074,0.6715,0.0011</t>
   </si>
   <si>
     <t>0.0001,0.0000,1.0000,0.0000</t>
@@ -1501,13 +1510,13 @@
     <t>0.0175,0.0026,0.9831,0.0012</t>
   </si>
   <si>
-    <t>0.4905,0.0312,0.3317,0.0063</t>
-  </si>
-  <si>
-    <t>0.9510,0.0005,0.0305,0.0002</t>
-  </si>
-  <si>
-    <t>0.8777,0.0004,0.0780,0.0006</t>
+    <t>0.4903,0.0312,0.3319,0.0063</t>
+  </si>
+  <si>
+    <t>0.9509,0.0005,0.0306,0.0002</t>
+  </si>
+  <si>
+    <t>0.8775,0.0004,0.0781,0.0006</t>
   </si>
   <si>
     <t>0.9891,0.0023,0.0020,0.0000</t>
@@ -1522,7 +1531,7 @@
     <t>0.9985,0.0003,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.9950,0.0023,0.0008,0.0000</t>
+    <t>0.9949,0.0023,0.0009,0.0000</t>
   </si>
   <si>
     <t>0.9952,0.0001,0.0018,0.0001</t>
@@ -1537,7 +1546,7 @@
     <t>0.9973,0.0004,0.0007,0.0000</t>
   </si>
   <si>
-    <t>0.0542,0.0388,0.8505,0.0009</t>
+    <t>0.0542,0.0389,0.8505,0.0009</t>
   </si>
   <si>
     <t>0.0058,0.0039,0.9946,0.0002</t>
@@ -1546,16 +1555,16 @@
     <t>0.0110,0.0042,0.9898,0.0004</t>
   </si>
   <si>
-    <t>0.2632,0.0234,0.5278,0.0015</t>
-  </si>
-  <si>
-    <t>0.1365,0.0003,0.9132,0.0003</t>
-  </si>
-  <si>
-    <t>0.8804,0.0220,0.0217,0.0037</t>
-  </si>
-  <si>
-    <t>0.5930,0.0460,0.1999,0.0050</t>
+    <t>0.2629,0.0234,0.5281,0.0015</t>
+  </si>
+  <si>
+    <t>0.1362,0.0003,0.9133,0.0003</t>
+  </si>
+  <si>
+    <t>0.8803,0.0220,0.0217,0.0037</t>
+  </si>
+  <si>
+    <t>0.5924,0.0460,0.2005,0.0050</t>
   </si>
   <si>
     <t>0.0053,0.0004,0.9961,0.0010</t>
@@ -1567,16 +1576,16 @@
     <t>0.0061,0.0004,0.0003,0.9989</t>
   </si>
   <si>
-    <t>0.0772,0.0002,0.0041,0.9688</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0443,0.9997</t>
+    <t>0.0771,0.0002,0.0041,0.9689</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0444,0.9997</t>
   </si>
   <si>
     <t>0.0029,0.0000,0.0009,0.9994</t>
   </si>
   <si>
-    <t>0.8978,0.0020,0.0184,0.0335</t>
+    <t>0.8976,0.0020,0.0184,0.0336</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1971,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1985,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1990,7 +1999,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2013,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2027,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2041,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2055,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2069,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2083,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2097,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2111,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2125,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2130,7 +2139,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,10 +2150,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2158,7 +2167,7 @@
         <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,10 +2178,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,7 +2195,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,10 +2206,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,10 +2220,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,10 +2234,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,10 +2248,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,10 +2262,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2270,7 +2279,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,10 +2304,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,10 +2318,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,10 +2332,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,10 +2346,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,10 +2360,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2368,7 +2377,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2382,7 +2391,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,10 +2402,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,10 +2416,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2424,7 +2433,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2438,7 +2447,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2452,7 +2461,7 @@
         <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,10 +2472,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,10 +2500,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,10 +2514,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,10 +2528,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,10 +2542,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,10 +2556,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,10 +2570,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,10 +2598,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,10 +2612,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,10 +2626,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,10 +2640,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,10 +2654,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,10 +2668,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,10 +2682,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,10 +2696,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,10 +2710,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2727,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2741,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2755,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2769,7 @@
         <v>264</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2783,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2797,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2811,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,10 +2822,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,10 +2836,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,10 +2850,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D65" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,10 +2864,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,10 +2878,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D67" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,10 +2892,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,10 +2906,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2914,7 +2923,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2928,7 +2937,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,10 +2948,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D72" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,10 +2962,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,10 +2976,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,10 +2990,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,10 +3004,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3021,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3035,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3049,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3063,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3077,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3091,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,10 +3102,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,10 +3116,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,10 +3144,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,10 +3158,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,10 +3172,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3189,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3203,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3217,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3231,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3245,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3259,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3273,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3287,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3301,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3315,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3329,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3343,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3357,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3371,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3385,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3399,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,10 +3410,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D105" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,10 +3424,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3441,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3455,7 @@
         <v>264</v>
       </c>
       <c r="D108" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,10 +3466,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,10 +3480,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,10 +3494,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D111" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,10 +3508,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,10 +3522,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D113" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,10 +3536,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3544,7 +3553,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3558,7 +3567,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,10 +3578,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D117" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3586,7 +3595,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3600,7 +3609,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,10 +3620,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D120" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,10 +3634,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D121" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,10 +3648,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D122" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,10 +3662,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D123" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,10 +3676,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,10 +3690,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D125" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D126" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,10 +3718,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D127" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3735,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3749,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3763,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3777,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3791,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3805,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3819,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3833,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,10 +3844,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,10 +3858,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D137" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,10 +3872,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D138" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,10 +3886,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D139" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3903,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3917,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3922,7 +3931,7 @@
         <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,7 +3945,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3959,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3973,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3987,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +4001,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,10 +4012,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4029,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,10 +4040,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D150" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4057,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,10 +4068,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D152" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4085,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,10 +4096,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D154" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,10 +4110,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D155" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,10 +4124,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D156" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4132,7 +4141,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4146,7 +4155,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4160,7 +4169,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4183,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4197,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D162" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4225,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4239,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4253,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4267,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4281,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4295,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4309,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4323,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4337,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4351,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,10 +4362,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4384,7 +4393,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4398,7 +4407,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4421,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4435,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4449,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4454,7 +4463,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,10 +4474,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4491,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,10 +4502,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,10 +4516,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,10 +4530,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,10 +4544,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,10 +4558,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,10 +4572,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,10 +4586,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4594,7 +4603,7 @@
         <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4617,7 @@
         <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4622,7 +4631,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,10 +4642,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,10 +4670,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4678,7 +4687,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,7 +4701,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,10 +4712,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,10 +4726,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,7 +4743,7 @@
         <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4757,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4762,7 +4771,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,10 +4782,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4799,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4813,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,10 +4824,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4832,7 +4841,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,10 +4852,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,10 +4866,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,10 +4880,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,10 +4894,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,10 +4908,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4925,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4939,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4953,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4967,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4981,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4995,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5009,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5023,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,10 +5034,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5042,7 +5051,7 @@
         <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5065,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,10 +5076,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,10 +5090,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,10 +5104,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,10 +5118,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,10 +5132,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,10 +5146,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,10 +5160,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,10 +5174,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5182,7 +5191,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5196,7 +5205,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5219,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5233,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5247,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5261,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5275,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5289,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5303,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5317,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5331,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,10 +5342,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,10 +5356,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,10 +5370,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,10 +5384,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,10 +5398,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5406,7 +5415,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5429,7 @@
         <v>264</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,10 +5440,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5448,7 +5457,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5471,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5485,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5499,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5513,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5518,7 +5527,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
